--- a/formlar/4. Yıkama Bölümü (ERTELENDİ)/EMS.WS.RPR.04.03. Sprey İşlem Günlük Üretim Raporu.xlsx
+++ b/formlar/4. Yıkama Bölümü (ERTELENDİ)/EMS.WS.RPR.04.03. Sprey İşlem Günlük Üretim Raporu.xlsx
@@ -206,7 +206,7 @@
     <t xml:space="preserve"> Approved By</t>
   </si>
   <si>
-    <t>EG.WS.RPR.04.03</t>
+    <t>EMS.WS.RPR.04.03</t>
   </si>
 </sst>
 </file>
